--- a/dist/test1.xlsx
+++ b/dist/test1.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Maga\Documents\GitHub\effective-rotary-phone\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Maga\Documents\GitHub\effective-rotary-phone\dist\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C4BC7CE-526D-4EA1-9F68-EB921B071D5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4994FBBD-E174-4AD1-865B-F690EF365DCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="14040" windowHeight="11295" xr2:uid="{3F48B126-E579-46B9-9E2B-BAA8564071F9}"/>
+    <workbookView xWindow="12150" yWindow="3420" windowWidth="14040" windowHeight="11295" xr2:uid="{3F48B126-E579-46B9-9E2B-BAA8564071F9}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="56">
   <si>
     <t>Ментальная (распознать/создать шаблон)</t>
   </si>
@@ -118,6 +118,90 @@
   </si>
   <si>
     <t>fill</t>
+  </si>
+  <si>
+    <t>Создаёт прямоугольник (Rect), размеры которого соответствуют изображению спрайта (self.image)., Устанавливает центр этого прямоугольника в указанные координаты (x, y).</t>
+  </si>
+  <si>
+    <t>Объект движется влево или вправо в зависимости от позиции (A, B, C или D), и всегда движется вниз.</t>
+  </si>
+  <si>
+    <t>хитбокс</t>
+  </si>
+  <si>
+    <t>Проверяется, совпадает ли изображение лягушки с типом гриба, и в зависимости от этого либо увеличивается счёт, либо отнимается жизнь.</t>
+  </si>
+  <si>
+    <t>Если изображение лягушки не совпадает с типом гриба, с которым произошло столкновение.</t>
+  </si>
+  <si>
+    <t>spritecollide</t>
+  </si>
+  <si>
+    <t>Инициализируется объект-спрайт: загружается изображение, задаётся прямоугольник с центром, устанавливаются начальные значения характеристик.</t>
+  </si>
+  <si>
+    <t>Изображение, прямоугольник, здоровье (health), сон (sleep), сытость (food) и счёт (score).</t>
+  </si>
+  <si>
+    <t>Вызывается конструктор родительского класса Sprite и загружается изображение для спрайта.</t>
+  </si>
+  <si>
+    <t>Создаётся спрайт шкалы: загружается изображение, задаётся позиция, выбирается тип иконок и создаётся список иконок в количестве start_param.</t>
+  </si>
+  <si>
+    <t>update</t>
+  </si>
+  <si>
+    <t>Для обработки события нажатия кнопки мыши.</t>
+  </si>
+  <si>
+    <t>Для обработки события закрытия окна игры (например, нажатие на крестик).</t>
+  </si>
+  <si>
+    <t>quit</t>
+  </si>
+  <si>
+    <t>Временная смена фона, отображение довольного состояния персонажа, задержка, возврат фона и изменение параметров (здоровье, сон, еда).</t>
+  </si>
+  <si>
+    <t>Здоровье +2, сон -1, еда -1</t>
+  </si>
+  <si>
+    <t>При выходе из паузы корректируется время начала игры, чтобы вычесть время, проведённое в паузе.</t>
+  </si>
+  <si>
+    <t>Восстанавливается стандартный игровой экран: отрисовывается фон, инициализируются кнопки, шкалы, персонаж и счёт, обновляется экран, и игра выходит из режима паузы.</t>
+  </si>
+  <si>
+    <t>get_ticks</t>
+  </si>
+  <si>
+    <t>Процесс создания визуальных компонентов игры: фонов, персонажей, интерфейса, анимации и других графических элементов.</t>
+  </si>
+  <si>
+    <t>Передаёт эмоции и атмосферу, помогает расставить акценты и направить внимание игрока.</t>
+  </si>
+  <si>
+    <t>фон</t>
+  </si>
+  <si>
+    <t>Потому что спрайты похожи на призраков, которые парят поверх данных, но не влияют на них.</t>
+  </si>
+  <si>
+    <t>Сначала в простых 2D-играх, затем и в 3D- и псевдо-3D играх.</t>
+  </si>
+  <si>
+    <t>полигон</t>
+  </si>
+  <si>
+    <t>Стиль рисования, использующий маленькие разноцветные квадраты (пиксели) для создания изображений.</t>
+  </si>
+  <si>
+    <t>Векторный редактор работает с графическими объектами, хранящимися как точные математические описания, а не набор пикселей.</t>
+  </si>
+  <si>
+    <t>пиксель-арт</t>
   </si>
 </sst>
 </file>
@@ -470,7 +554,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{137B1794-2259-47ED-86A7-63615F2F1F7C}">
-  <dimension ref="A1:C30"/>
+  <dimension ref="A1:C60"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="58.28515625" customWidth="1"/>
@@ -806,7 +890,338 @@
         <v>27</v>
       </c>
     </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>1889</v>
+      </c>
+      <c r="B31">
+        <v>1201815</v>
+      </c>
+      <c r="C31" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>1889</v>
+      </c>
+      <c r="B32">
+        <v>1201817</v>
+      </c>
+      <c r="C32" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>1889</v>
+      </c>
+      <c r="B33">
+        <v>1201818</v>
+      </c>
+      <c r="C33" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>1890</v>
+      </c>
+      <c r="B34">
+        <v>1201824</v>
+      </c>
+      <c r="C34" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>1890</v>
+      </c>
+      <c r="B35">
+        <v>1201826</v>
+      </c>
+      <c r="C35" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <v>1890</v>
+      </c>
+      <c r="B36">
+        <v>1201827</v>
+      </c>
+      <c r="C36" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <v>1891</v>
+      </c>
+      <c r="B37">
+        <v>1201828</v>
+      </c>
+      <c r="C37" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <v>1891</v>
+      </c>
+      <c r="B38">
+        <v>1201829</v>
+      </c>
+      <c r="C38" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39">
+        <v>1891</v>
+      </c>
+      <c r="B39">
+        <v>1201830</v>
+      </c>
+      <c r="C39">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40">
+        <v>1892</v>
+      </c>
+      <c r="B40">
+        <v>1201833</v>
+      </c>
+      <c r="C40" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41">
+        <v>1892</v>
+      </c>
+      <c r="B41">
+        <v>1201834</v>
+      </c>
+      <c r="C41" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42">
+        <v>1892</v>
+      </c>
+      <c r="B42">
+        <v>1201835</v>
+      </c>
+      <c r="C42" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43">
+        <v>1893</v>
+      </c>
+      <c r="B43">
+        <v>1201838</v>
+      </c>
+      <c r="C43" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44">
+        <v>1893</v>
+      </c>
+      <c r="B44">
+        <v>1201839</v>
+      </c>
+      <c r="C44" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45">
+        <v>1893</v>
+      </c>
+      <c r="B45">
+        <v>1201843</v>
+      </c>
+      <c r="C45" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46">
+        <v>1894</v>
+      </c>
+      <c r="B46">
+        <v>1201853</v>
+      </c>
+      <c r="C46" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A47">
+        <v>1894</v>
+      </c>
+      <c r="B47">
+        <v>1201856</v>
+      </c>
+      <c r="C47" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A48">
+        <v>1894</v>
+      </c>
+      <c r="B48">
+        <v>1201859</v>
+      </c>
+      <c r="C48" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49">
+        <v>1895</v>
+      </c>
+      <c r="B49">
+        <v>1201868</v>
+      </c>
+      <c r="C49" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50">
+        <v>1895</v>
+      </c>
+      <c r="B50">
+        <v>1201869</v>
+      </c>
+      <c r="C50" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51">
+        <v>1895</v>
+      </c>
+      <c r="B51">
+        <v>1201870</v>
+      </c>
+      <c r="C51" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52">
+        <v>1896</v>
+      </c>
+      <c r="B52">
+        <v>1201876</v>
+      </c>
+      <c r="C52" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A53">
+        <v>1896</v>
+      </c>
+      <c r="B53">
+        <v>1201877</v>
+      </c>
+      <c r="C53" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A54">
+        <v>1896</v>
+      </c>
+      <c r="B54">
+        <v>1201880</v>
+      </c>
+      <c r="C54" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A55">
+        <v>1897</v>
+      </c>
+      <c r="B55">
+        <v>1201889</v>
+      </c>
+      <c r="C55" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A56">
+        <v>1897</v>
+      </c>
+      <c r="B56">
+        <v>1201890</v>
+      </c>
+      <c r="C56" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A57">
+        <v>1897</v>
+      </c>
+      <c r="B57">
+        <v>1201892</v>
+      </c>
+      <c r="C57" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58">
+        <v>1898</v>
+      </c>
+      <c r="B58">
+        <v>1201903</v>
+      </c>
+      <c r="C58" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A59">
+        <v>1898</v>
+      </c>
+      <c r="B59">
+        <v>1201904</v>
+      </c>
+      <c r="C59" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A60">
+        <v>1898</v>
+      </c>
+      <c r="B60">
+        <v>1201906</v>
+      </c>
+      <c r="C60" t="s">
+        <v>55</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
--- a/dist/test1.xlsx
+++ b/dist/test1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Maga\Documents\GitHub\effective-rotary-phone\dist\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4994FBBD-E174-4AD1-865B-F690EF365DCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E823C308-28DF-47D4-8F8F-14631D8FF8C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12150" yWindow="3420" windowWidth="14040" windowHeight="11295" xr2:uid="{3F48B126-E579-46B9-9E2B-BAA8564071F9}"/>
+    <workbookView xWindow="8550" yWindow="3045" windowWidth="14040" windowHeight="11295" xr2:uid="{3F48B126-E579-46B9-9E2B-BAA8564071F9}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -34,184 +34,199 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="56">
-  <si>
-    <t>Ментальная (распознать/создать шаблон)</t>
-  </si>
-  <si>
-    <t>Комбинирование механик из разных жанров</t>
-  </si>
-  <si>
-    <t>отнять</t>
-  </si>
-  <si>
-    <t>…расстояние между трубами сокращается, а скорость полета увеличивается.</t>
-  </si>
-  <si>
-    <t>кривая сложности</t>
-  </si>
-  <si>
-    <t>Геймплей, нарративный дизайн и сюжет</t>
-  </si>
-  <si>
-    <t>Исследователи</t>
-  </si>
-  <si>
-    <t>синтез</t>
-  </si>
-  <si>
-    <t>Консистентность (единобразие)</t>
-  </si>
-  <si>
-    <t>3D-модель главного героя, бегущего по полю</t>
-  </si>
-  <si>
-    <t>разметка</t>
-  </si>
-  <si>
-    <t>Последовательность шагов и действий, которые пользователь проходит при взаимодействии с продуктом (сайтом, игрой).</t>
-  </si>
-  <si>
-    <t>Потому что это позволяет найти и исправить ошибки и неудобства, которые не заметили сами разработчики, и сделать продукт удобным для всех.</t>
-  </si>
-  <si>
-    <t>Интересно поиграть в игру, которую придумал одноклассник.</t>
-  </si>
-  <si>
-    <t>Ответить на ключевые вопросы об этапах взаимодействия пользователя с игрой, найти недостающие или слабые места.</t>
-  </si>
-  <si>
-    <t>аудитория</t>
-  </si>
-  <si>
-    <t>Рендеринг</t>
-  </si>
-  <si>
-    <t>pygame.time</t>
-  </si>
-  <si>
-    <t>игровой цикл</t>
-  </si>
-  <si>
-    <t>При касании границы значение self.direction умножается на -1, меняя знак скорости по оси X.</t>
-  </si>
-  <si>
-    <t>clock.tick(60)</t>
-  </si>
-  <si>
-    <t>screen</t>
-  </si>
-  <si>
-    <t>В методе update сравнивается разница между текущим временем (pygame.tick.get_ticks()) и временем последнего перемещения (self.move_timer).</t>
-  </si>
-  <si>
-    <t>pygame.transform.scale()</t>
-  </si>
-  <si>
-    <t>blit</t>
-  </si>
-  <si>
-    <t>pygame.KEYDOWN</t>
-  </si>
-  <si>
-    <t>Переменная-флаг active у всех кнопок устанавливается в False, и они становятся серыми.</t>
-  </si>
-  <si>
-    <t>fill</t>
-  </si>
-  <si>
-    <t>Создаёт прямоугольник (Rect), размеры которого соответствуют изображению спрайта (self.image)., Устанавливает центр этого прямоугольника в указанные координаты (x, y).</t>
-  </si>
-  <si>
-    <t>Объект движется влево или вправо в зависимости от позиции (A, B, C или D), и всегда движется вниз.</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="58">
   <si>
     <t>хитбокс</t>
   </si>
   <si>
-    <t>Проверяется, совпадает ли изображение лягушки с типом гриба, и в зависимости от этого либо увеличивается счёт, либо отнимается жизнь.</t>
-  </si>
-  <si>
-    <t>Если изображение лягушки не совпадает с типом гриба, с которым произошло столкновение.</t>
-  </si>
-  <si>
-    <t>spritecollide</t>
-  </si>
-  <si>
-    <t>Инициализируется объект-спрайт: загружается изображение, задаётся прямоугольник с центром, устанавливаются начальные значения характеристик.</t>
-  </si>
-  <si>
-    <t>Изображение, прямоугольник, здоровье (health), сон (sleep), сытость (food) и счёт (score).</t>
-  </si>
-  <si>
-    <t>Вызывается конструктор родительского класса Sprite и загружается изображение для спрайта.</t>
-  </si>
-  <si>
-    <t>Создаётся спрайт шкалы: загружается изображение, задаётся позиция, выбирается тип иконок и создаётся список иконок в количестве start_param.</t>
-  </si>
-  <si>
-    <t>update</t>
-  </si>
-  <si>
-    <t>Для обработки события нажатия кнопки мыши.</t>
-  </si>
-  <si>
-    <t>Для обработки события закрытия окна игры (например, нажатие на крестик).</t>
-  </si>
-  <si>
-    <t>quit</t>
-  </si>
-  <si>
-    <t>Временная смена фона, отображение довольного состояния персонажа, задержка, возврат фона и изменение параметров (здоровье, сон, еда).</t>
-  </si>
-  <si>
-    <t>Здоровье +2, сон -1, еда -1</t>
-  </si>
-  <si>
-    <t>При выходе из паузы корректируется время начала игры, чтобы вычесть время, проведённое в паузе.</t>
-  </si>
-  <si>
-    <t>Восстанавливается стандартный игровой экран: отрисовывается фон, инициализируются кнопки, шкалы, персонаж и счёт, обновляется экран, и игра выходит из режима паузы.</t>
-  </si>
-  <si>
-    <t>get_ticks</t>
-  </si>
-  <si>
-    <t>Процесс создания визуальных компонентов игры: фонов, персонажей, интерфейса, анимации и других графических элементов.</t>
-  </si>
-  <si>
-    <t>Передаёт эмоции и атмосферу, помогает расставить акценты и направить внимание игрока.</t>
-  </si>
-  <si>
-    <t>фон</t>
-  </si>
-  <si>
-    <t>Потому что спрайты похожи на призраков, которые парят поверх данных, но не влияют на них.</t>
-  </si>
-  <si>
-    <t>Сначала в простых 2D-играх, затем и в 3D- и псевдо-3D играх.</t>
-  </si>
-  <si>
-    <t>полигон</t>
-  </si>
-  <si>
-    <t>Стиль рисования, использующий маленькие разноцветные квадраты (пиксели) для создания изображений.</t>
-  </si>
-  <si>
-    <t>Векторный редактор работает с графическими объектами, хранящимися как точные математические описания, а не набор пикселей.</t>
-  </si>
-  <si>
-    <t>пиксель-арт</t>
+    <t>button.rect</t>
+  </si>
+  <si>
+    <t>Чтобы логику "убегания" при наведении курсора можно было применить только к кнопке "Играть", а не к кнопке "Учиться".</t>
+  </si>
+  <si>
+    <t>draw_text</t>
+  </si>
+  <si>
+    <t>Кастомизация</t>
+  </si>
+  <si>
+    <t>Полный пароль от личного кабинета персонажа.</t>
+  </si>
+  <si>
+    <t>концепт-арт</t>
+  </si>
+  <si>
+    <t>Открытые локации (города, леса, космос).</t>
+  </si>
+  <si>
+    <t>Отсутствие стилистического единства с вашим проектом.</t>
+  </si>
+  <si>
+    <t>Пустые</t>
+  </si>
+  <si>
+    <t>Шкала</t>
+  </si>
+  <si>
+    <t>Создать для кнопок дополнительное графическое состояние (например, "отжатый" вид).</t>
+  </si>
+  <si>
+    <t>Кнопки «Включить музыку» и «Выключить музыку».</t>
+  </si>
+  <si>
+    <t>Отсчет времени останавливается, а основные игровые кнопки становятся неактивны.</t>
+  </si>
+  <si>
+    <t>Images</t>
+  </si>
+  <si>
+    <t>Игровой персонаж Кукурузмен</t>
+  </si>
+  <si>
+    <t>Используется переменная-флаг (например, show_exit_button), значение которой проверяется в цикле отрисовки.</t>
+  </si>
+  <si>
+    <t>Функция play_game возвращает значение False, что приводит к выходу из её цикла и возврату в главное меню.</t>
+  </si>
+  <si>
+    <t>Для комфортного перехода на другие экраны (чтобы избежать случайных множественных кликов).</t>
+  </si>
+  <si>
+    <t>цикл</t>
+  </si>
+  <si>
+    <t>Чтобы платформа не выходила за верхнюю и нижнюю границы игрового окна.</t>
+  </si>
+  <si>
+    <t>Левая платформа управляется клавишами W и S, правая — стрелками «вверх» и «вниз».</t>
+  </si>
+  <si>
+    <t>collision</t>
+  </si>
+  <si>
+    <t>С помощью оператора return, который завершает всю функцию.</t>
+  </si>
+  <si>
+    <t>Удаляет спрайт из всех групп спрайтов, к которым он принадлежит.</t>
+  </si>
+  <si>
+    <t>target</t>
+  </si>
+  <si>
+    <t>Шкалы сна, здоровья и голода</t>
+  </si>
+  <si>
+    <t>main.py и mouseclick.py</t>
+  </si>
+  <si>
+    <t>const</t>
+  </si>
+  <si>
+    <t>.play()</t>
+  </si>
+  <si>
+    <t>Загружает звуковой файл в объект</t>
+  </si>
+  <si>
+    <t>Небольшой оцифрованный звуковой фрагмент</t>
+  </si>
+  <si>
+    <t>Приставки, поддерживающие пять каналов звука</t>
+  </si>
+  <si>
+    <t>сэмплирование</t>
+  </si>
+  <si>
+    <t>Общее представление о саундтреке</t>
+  </si>
+  <si>
+    <t>экспликация</t>
+  </si>
+  <si>
+    <t>Создавать интересные аранжировки и раскрывать творческий потенциал</t>
+  </si>
+  <si>
+    <t>Она улучшает мастерство и уверенность в работе с программой.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> вокалоид</t>
+  </si>
+  <si>
+    <t>Эффекты, вызванные действиями игрока или движением игровых персонажей.</t>
+  </si>
+  <si>
+    <t>Пассивные звуковые эффекты.</t>
+  </si>
+  <si>
+    <t>Состояния</t>
+  </si>
+  <si>
+    <t>Чек-лист нужен для систематизации элементов звукового дизайна и отслеживания прогресса их готовности.</t>
+  </si>
+  <si>
+    <t>Помогают упростить поиск необходимых звуков среди множества аудиофайлов.</t>
+  </si>
+  <si>
+    <t>тег</t>
+  </si>
+  <si>
+    <t>Аудиофайлы (саундтрек и звуковые эффекты)</t>
+  </si>
+  <si>
+    <t>Создавать дополнительные спрайты, фоны и звуки, экспериментировать.</t>
+  </si>
+  <si>
+    <t>sounds</t>
+  </si>
+  <si>
+    <t>Список лучших выполненных специалистом работ.</t>
+  </si>
+  <si>
+    <t>Подробное резюме о предыдущем месте работы.</t>
+  </si>
+  <si>
+    <t>Акселератор</t>
+  </si>
+  <si>
+    <t>Процесс внутри установленных правил, целью которого является сам процесс.</t>
+  </si>
+  <si>
+    <t>Стратегий принятия решений в условиях конкуренции.</t>
+  </si>
+  <si>
+    <t>проигрышная</t>
+  </si>
+  <si>
+    <t>Положение, когда игрок гарантированно выиграет, несмотря на действия соперника.</t>
+  </si>
+  <si>
+    <t>Проигрышная стратегия</t>
+  </si>
+  <si>
+    <t>or</t>
+  </si>
+  <si>
+    <t>Приключенческий экшен -&gt; Энергичная и быстрая музыка, которая звучит во время моментов преследования и активных действий в игре.,
+Фэнтезийный  экшен -&gt; Вводная часть игры, формирующая настроение неразгаданных тайн и скрытых смыслов.,
+Выживание  в открытом море -&gt; Спокойная и умиротворяющая мелодия, сопровождающая первые моменты морского путешествия на судне или небольшой лодке.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="204"/>
@@ -238,8 +253,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -562,373 +582,373 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1">
-        <v>1879</v>
+        <v>1899</v>
       </c>
       <c r="B1">
-        <v>1201475</v>
+        <v>1203891</v>
       </c>
       <c r="C1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>1879</v>
-      </c>
-      <c r="B2">
-        <v>1201476</v>
-      </c>
-      <c r="C2" t="s">
-        <v>1</v>
+        <v>1899</v>
+      </c>
+      <c r="B2" s="1">
+        <v>1203892</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>1879</v>
-      </c>
-      <c r="B3">
-        <v>1201477</v>
+        <v>1899</v>
+      </c>
+      <c r="B3" s="1">
+        <v>1203893</v>
       </c>
       <c r="C3" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>1880</v>
+        <v>1900</v>
       </c>
       <c r="B4">
-        <v>1201480</v>
-      </c>
-      <c r="C4">
-        <v>10</v>
+        <v>1203897</v>
+      </c>
+      <c r="C4" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>1880</v>
+        <v>1900</v>
       </c>
       <c r="B5">
-        <v>1201481</v>
+        <v>1203898</v>
       </c>
       <c r="C5" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>1880</v>
+        <v>1900</v>
       </c>
       <c r="B6">
-        <v>1201482</v>
+        <v>1203899</v>
       </c>
       <c r="C6" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>1881</v>
+        <v>1901</v>
       </c>
       <c r="B7">
-        <v>1201485</v>
+        <v>1203902</v>
       </c>
       <c r="C7" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>1881</v>
+        <v>1901</v>
       </c>
       <c r="B8">
-        <v>1201486</v>
+        <v>1203903</v>
       </c>
       <c r="C8" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>1881</v>
+        <v>1901</v>
       </c>
       <c r="B9">
-        <v>1201487</v>
+        <v>1203904</v>
       </c>
       <c r="C9" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10">
-        <v>1882</v>
+        <v>1902</v>
       </c>
       <c r="B10">
-        <v>1201490</v>
+        <v>1203907</v>
       </c>
       <c r="C10" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>1882</v>
+        <v>1902</v>
       </c>
       <c r="B11">
-        <v>1201491</v>
+        <v>1203908</v>
       </c>
       <c r="C11" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>1882</v>
+        <v>1902</v>
       </c>
       <c r="B12">
-        <v>1201492</v>
-      </c>
-      <c r="C12" t="s">
-        <v>10</v>
+        <v>1203909</v>
+      </c>
+      <c r="C12">
+        <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13">
-        <v>1883</v>
+        <v>1903</v>
       </c>
       <c r="B13">
-        <v>1201495</v>
+        <v>1203912</v>
       </c>
       <c r="C13" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14">
-        <v>1883</v>
+        <v>1903</v>
       </c>
       <c r="B14">
-        <v>1201497</v>
+        <v>1203913</v>
       </c>
       <c r="C14" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15">
-        <v>1883</v>
+        <v>1903</v>
       </c>
       <c r="B15">
-        <v>1201498</v>
-      </c>
-      <c r="C15">
-        <v>256</v>
+        <v>1203914</v>
+      </c>
+      <c r="C15" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16">
-        <v>1884</v>
+        <v>1904</v>
       </c>
       <c r="B16">
-        <v>1201501</v>
+        <v>1203983</v>
       </c>
       <c r="C16" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17">
-        <v>1884</v>
+        <v>1904</v>
       </c>
       <c r="B17">
-        <v>1201502</v>
+        <v>1203985</v>
       </c>
       <c r="C17" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18">
-        <v>1884</v>
+        <v>1904</v>
       </c>
       <c r="B18">
-        <v>1201503</v>
+        <v>1203988</v>
       </c>
       <c r="C18" t="s">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19">
-        <v>1885</v>
+        <v>1905</v>
       </c>
       <c r="B19">
-        <v>1201507</v>
+        <v>1203993</v>
       </c>
       <c r="C19" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20">
-        <v>1885</v>
+        <v>1905</v>
       </c>
       <c r="B20">
-        <v>1201508</v>
+        <v>1203996</v>
       </c>
       <c r="C20" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21">
-        <v>1885</v>
+        <v>1905</v>
       </c>
       <c r="B21">
-        <v>1201509</v>
+        <v>1203997</v>
       </c>
       <c r="C21" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22">
-        <v>1886</v>
+        <v>1906</v>
       </c>
       <c r="B22">
-        <v>1201512</v>
+        <v>1204005</v>
       </c>
       <c r="C22" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23">
-        <v>1886</v>
+        <v>1906</v>
       </c>
       <c r="B23">
-        <v>1201514</v>
+        <v>1204008</v>
       </c>
       <c r="C23" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24">
-        <v>1886</v>
+        <v>1906</v>
       </c>
       <c r="B24">
-        <v>1201515</v>
+        <v>1204009</v>
       </c>
       <c r="C24" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25">
-        <v>1887</v>
+        <v>1907</v>
       </c>
       <c r="B25">
-        <v>1201518</v>
+        <v>1204015</v>
       </c>
       <c r="C25" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26">
-        <v>1887</v>
+        <v>1907</v>
       </c>
       <c r="B26">
-        <v>1201519</v>
+        <v>1204017</v>
       </c>
       <c r="C26" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27">
-        <v>1887</v>
+        <v>1907</v>
       </c>
       <c r="B27">
-        <v>1201520</v>
+        <v>1204020</v>
       </c>
       <c r="C27" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28">
-        <v>1888</v>
+        <v>1908</v>
       </c>
       <c r="B28">
-        <v>1201523</v>
+        <v>1204024</v>
       </c>
       <c r="C28" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29">
-        <v>1888</v>
+        <v>1908</v>
       </c>
       <c r="B29">
-        <v>1201524</v>
+        <v>1204025</v>
       </c>
       <c r="C29" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30">
-        <v>1888</v>
+        <v>1908</v>
       </c>
       <c r="B30">
-        <v>1201525</v>
+        <v>1204027</v>
       </c>
       <c r="C30" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31">
-        <v>1889</v>
+        <v>1909</v>
       </c>
       <c r="B31">
-        <v>1201815</v>
+        <v>1205629</v>
       </c>
       <c r="C31" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32">
-        <v>1889</v>
+        <v>1909</v>
       </c>
       <c r="B32">
-        <v>1201817</v>
+        <v>1205630</v>
       </c>
       <c r="C32" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33">
-        <v>1889</v>
+        <v>1909</v>
       </c>
       <c r="B33">
-        <v>1201818</v>
-      </c>
-      <c r="C33" t="s">
-        <v>30</v>
+        <v>1205632</v>
+      </c>
+      <c r="C33">
+        <v>6</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34">
-        <v>1890</v>
+        <v>1910</v>
       </c>
       <c r="B34">
-        <v>1201824</v>
+        <v>1205635</v>
       </c>
       <c r="C34" t="s">
         <v>31</v>
@@ -936,10 +956,10 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35">
-        <v>1890</v>
+        <v>1910</v>
       </c>
       <c r="B35">
-        <v>1201826</v>
+        <v>1205636</v>
       </c>
       <c r="C35" t="s">
         <v>32</v>
@@ -947,54 +967,54 @@
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36">
-        <v>1890</v>
+        <v>1910</v>
       </c>
       <c r="B36">
-        <v>1201827</v>
+        <v>1205637</v>
       </c>
       <c r="C36" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3" ht="135" x14ac:dyDescent="0.25">
       <c r="A37">
-        <v>1891</v>
+        <v>1911</v>
       </c>
       <c r="B37">
-        <v>1201828</v>
-      </c>
-      <c r="C37" t="s">
-        <v>34</v>
+        <v>1205640</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38">
-        <v>1891</v>
+        <v>1911</v>
       </c>
       <c r="B38">
-        <v>1201829</v>
+        <v>1205642</v>
       </c>
       <c r="C38" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39">
-        <v>1891</v>
+        <v>1911</v>
       </c>
       <c r="B39">
-        <v>1201830</v>
-      </c>
-      <c r="C39">
-        <v>3</v>
+        <v>1205643</v>
+      </c>
+      <c r="C39" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40">
-        <v>1892</v>
+        <v>1912</v>
       </c>
       <c r="B40">
-        <v>1201833</v>
+        <v>1205648</v>
       </c>
       <c r="C40" t="s">
         <v>36</v>
@@ -1002,10 +1022,10 @@
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41">
-        <v>1892</v>
+        <v>1912</v>
       </c>
       <c r="B41">
-        <v>1201834</v>
+        <v>1205649</v>
       </c>
       <c r="C41" t="s">
         <v>37</v>
@@ -1013,10 +1033,10 @@
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42">
-        <v>1892</v>
+        <v>1912</v>
       </c>
       <c r="B42">
-        <v>1201835</v>
+        <v>1205650</v>
       </c>
       <c r="C42" t="s">
         <v>38</v>
@@ -1024,10 +1044,10 @@
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43">
-        <v>1893</v>
+        <v>1913</v>
       </c>
       <c r="B43">
-        <v>1201838</v>
+        <v>1205654</v>
       </c>
       <c r="C43" t="s">
         <v>39</v>
@@ -1035,10 +1055,10 @@
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44">
-        <v>1893</v>
+        <v>1913</v>
       </c>
       <c r="B44">
-        <v>1201839</v>
+        <v>1205655</v>
       </c>
       <c r="C44" t="s">
         <v>40</v>
@@ -1046,10 +1066,10 @@
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45">
-        <v>1893</v>
+        <v>1913</v>
       </c>
       <c r="B45">
-        <v>1201843</v>
+        <v>1205656</v>
       </c>
       <c r="C45" t="s">
         <v>41</v>
@@ -1057,10 +1077,10 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46">
-        <v>1894</v>
+        <v>1914</v>
       </c>
       <c r="B46">
-        <v>1201853</v>
+        <v>1205659</v>
       </c>
       <c r="C46" t="s">
         <v>42</v>
@@ -1068,10 +1088,10 @@
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47">
-        <v>1894</v>
+        <v>1914</v>
       </c>
       <c r="B47">
-        <v>1201856</v>
+        <v>1205660</v>
       </c>
       <c r="C47" t="s">
         <v>43</v>
@@ -1079,145 +1099,145 @@
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48">
-        <v>1894</v>
+        <v>1914</v>
       </c>
       <c r="B48">
-        <v>1201859</v>
+        <v>1205661</v>
       </c>
       <c r="C48" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49">
-        <v>1895</v>
+        <v>1915</v>
       </c>
       <c r="B49">
-        <v>1201868</v>
+        <v>1205665</v>
       </c>
       <c r="C49" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50">
-        <v>1895</v>
+        <v>1915</v>
       </c>
       <c r="B50">
-        <v>1201869</v>
+        <v>1205666</v>
       </c>
       <c r="C50" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51">
-        <v>1895</v>
+        <v>1915</v>
       </c>
       <c r="B51">
-        <v>1201870</v>
+        <v>1205667</v>
       </c>
       <c r="C51" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52">
-        <v>1896</v>
+        <v>1916</v>
       </c>
       <c r="B52">
-        <v>1201876</v>
+        <v>1205670</v>
       </c>
       <c r="C52" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53">
-        <v>1896</v>
+        <v>1916</v>
       </c>
       <c r="B53">
-        <v>1201877</v>
+        <v>1205671</v>
       </c>
       <c r="C53" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54">
-        <v>1896</v>
+        <v>1916</v>
       </c>
       <c r="B54">
-        <v>1201880</v>
+        <v>1205672</v>
       </c>
       <c r="C54" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55">
-        <v>1897</v>
+        <v>1917</v>
       </c>
       <c r="B55">
-        <v>1201889</v>
+        <v>1205674</v>
       </c>
       <c r="C55" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56">
-        <v>1897</v>
+        <v>1917</v>
       </c>
       <c r="B56">
-        <v>1201890</v>
+        <v>1205675</v>
       </c>
       <c r="C56" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57">
-        <v>1897</v>
+        <v>1917</v>
       </c>
       <c r="B57">
-        <v>1201892</v>
+        <v>1205676</v>
       </c>
       <c r="C57" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58">
-        <v>1898</v>
+        <v>1918</v>
       </c>
       <c r="B58">
-        <v>1201903</v>
+        <v>1205677</v>
       </c>
       <c r="C58" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59">
-        <v>1898</v>
+        <v>1918</v>
       </c>
       <c r="B59">
-        <v>1201904</v>
+        <v>1205678</v>
       </c>
       <c r="C59" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60">
-        <v>1898</v>
+        <v>1918</v>
       </c>
       <c r="B60">
-        <v>1201906</v>
+        <v>1205681</v>
       </c>
       <c r="C60" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
   </sheetData>

--- a/dist/test1.xlsx
+++ b/dist/test1.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Maga\Documents\GitHub\effective-rotary-phone\dist\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Maga\Documents\GitHub\effective-rotary-phone\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E823C308-28DF-47D4-8F8F-14631D8FF8C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D131D76D-5AC1-4700-BCBA-6FA6AC2A9F7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="8550" yWindow="3045" windowWidth="14040" windowHeight="11295" xr2:uid="{3F48B126-E579-46B9-9E2B-BAA8564071F9}"/>
   </bookViews>
